--- a/student_assessment_forms/010_oral_skills_assessment_form--student_assessment_forms.xlsx
+++ b/student_assessment_forms/010_oral_skills_assessment_form--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>pronunciation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pronunciation</t>
+          <t>Pronunciation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>fluency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fluency</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>interaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vocabulary</t>
+          <t>Interaction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>interaction_1</t>
+          <t>interaction_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>Interaction 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>interaction_2</t>
+          <t>comprehension</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>interaction</t>
+          <t>Comprehension</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>vocabulary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>Vocabulary</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comprehension</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rating_6</t>
+          <t>vocabulary_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>vocabulary_2</t>
+          <t>Vocabulary_2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rating_7</t>
+          <t>vocabulary_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vocabulary_2</t>
+          <t>Vocabulary_3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating_8</t>
+          <t>extra_question</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>vocabulary_3</t>
+          <t>Extra question</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,68 +781,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>interaction_1_choices</t>
+          <t>interaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interaction_1_choices</t>
+          <t>interaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interaction_1_choices</t>
+          <t>interaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interaction_1_choices</t>
+          <t>interaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
